--- a/Res_ConvLSTM/DroughtDataset_model_testing_1754031464_h_3.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1754031464_h_3.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.01484579571423159</v>
+        <v>0.008388527301638544</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008425238155320435</v>
+        <v>0.008417747105701008</v>
       </c>
       <c r="C2" t="n">
-        <v>18888831</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>18888831</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>13814617</v>
+        <v>4600865</v>
       </c>
       <c r="L2" t="n">
-        <v>8243015</v>
+        <v>2744139</v>
       </c>
       <c r="M2" t="n">
-        <v>2094633</v>
+        <v>690209</v>
       </c>
       <c r="N2" t="n">
-        <v>110062</v>
+        <v>34370</v>
       </c>
       <c r="O2" t="n">
-        <v>1262104</v>
+        <v>418947</v>
       </c>
       <c r="P2" t="n">
-        <v>501780</v>
+        <v>165697</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999943971633911</v>
+        <v>0.9999882578849792</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9212570190429688</v>
+        <v>0.9181574583053589</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8252570629119873</v>
+        <v>0.8180971145629883</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7772486209869385</v>
+        <v>0.7760747075080872</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5892001390457153</v>
+        <v>0.5689737796783447</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8229386806488037</v>
+        <v>0.8170813322067261</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8786879181861877</v>
+        <v>0.8777486681938171</v>
       </c>
       <c r="X2" t="n">
-        <v>18888831</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,469 +742,469 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>18888831</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>14410974</v>
+        <v>4815402</v>
       </c>
       <c r="AG2" t="n">
-        <v>8878131</v>
+        <v>2970254</v>
       </c>
       <c r="AH2" t="n">
-        <v>2395233</v>
+        <v>799435</v>
       </c>
       <c r="AI2" t="n">
-        <v>176729</v>
+        <v>58995</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1376498</v>
+        <v>459097</v>
       </c>
       <c r="AK2" t="n">
-        <v>540046</v>
+        <v>180028</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9566605687141418</v>
+        <v>0.9565494656562805</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112324118614197</v>
+        <v>0.9113017320632935</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8581742644309998</v>
+        <v>0.8579359650611877</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6626757383346558</v>
+        <v>0.6623888611793518</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.902050256729126</v>
+        <v>0.9020065665245056</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314221143722534</v>
+        <v>0.9314266443252563</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.003519465909193775</v>
+        <v>0.001941229827729973</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002021116422987386</v>
+        <v>0.002018670822238358</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>13814617</v>
+        <v>4600865</v>
       </c>
       <c r="E3" t="n">
-        <v>1212902</v>
+        <v>423401</v>
       </c>
       <c r="F3" t="n">
-        <v>18302</v>
+        <v>3610</v>
       </c>
       <c r="G3" t="n">
-        <v>2342</v>
+        <v>612</v>
       </c>
       <c r="H3" t="n">
-        <v>734</v>
+        <v>203</v>
       </c>
       <c r="I3" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="J3" t="n">
-        <v>29970263</v>
+        <v>10016548</v>
       </c>
       <c r="K3" t="n">
-        <v>32629474</v>
+        <v>10890787</v>
       </c>
       <c r="L3" t="n">
-        <v>37358135</v>
+        <v>12455252</v>
       </c>
       <c r="M3" t="n">
-        <v>45466507</v>
+        <v>15198330</v>
       </c>
       <c r="N3" t="n">
-        <v>48515553</v>
+        <v>16214434</v>
       </c>
       <c r="O3" t="n">
-        <v>47061032</v>
+        <v>15726633</v>
       </c>
       <c r="P3" t="n">
-        <v>48210078</v>
+        <v>16113221</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9179791808128357</v>
+        <v>0.9149209856987</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8449470400810242</v>
+        <v>0.840679407119751</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7501211166381836</v>
+        <v>0.7404722571372986</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4123562276363373</v>
+        <v>0.3856208324432373</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8267325758934021</v>
+        <v>0.8227908611297607</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8653677105903625</v>
+        <v>0.8571968078613281</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>14410974</v>
+        <v>4815402</v>
       </c>
       <c r="Z3" t="n">
-        <v>591937</v>
+        <v>197896</v>
       </c>
       <c r="AA3" t="n">
-        <v>25520</v>
+        <v>8540</v>
       </c>
       <c r="AB3" t="n">
-        <v>20288</v>
+        <v>6789</v>
       </c>
       <c r="AC3" t="n">
-        <v>135</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>29970369</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>33157398</v>
+        <v>11082162</v>
       </c>
       <c r="AG3" t="n">
-        <v>38238679</v>
+        <v>12776309</v>
       </c>
       <c r="AH3" t="n">
-        <v>45670960</v>
+        <v>15265103</v>
       </c>
       <c r="AI3" t="n">
-        <v>48502329</v>
+        <v>16210402</v>
       </c>
       <c r="AJ3" t="n">
-        <v>47183115</v>
+        <v>15770546</v>
       </c>
       <c r="AK3" t="n">
-        <v>48239592</v>
+        <v>16123045</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576069712638855</v>
+        <v>0.957583487033844</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100493192672729</v>
+        <v>0.9099507331848145</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8577707409858704</v>
+        <v>0.8576524257659912</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6621295809745789</v>
+        <v>0.6619057655334473</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016655683517456</v>
+        <v>0.9016434550285339</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313610792160034</v>
+        <v>0.9313350915908813</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.044805300763648</v>
+        <v>0.02946928272075372</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03188647610643539</v>
+        <v>0.03186393749853683</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1116840</v>
+        <v>387400</v>
       </c>
       <c r="E4" t="n">
-        <v>8243015</v>
+        <v>2744139</v>
       </c>
       <c r="F4" t="n">
-        <v>366238</v>
+        <v>123878</v>
       </c>
       <c r="G4" t="n">
-        <v>8128</v>
+        <v>2503</v>
       </c>
       <c r="H4" t="n">
-        <v>20161</v>
+        <v>5960</v>
       </c>
       <c r="I4" t="n">
-        <v>1277</v>
+        <v>312</v>
       </c>
       <c r="J4" t="n">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="K4" t="n">
-        <v>1180782</v>
+        <v>410111</v>
       </c>
       <c r="L4" t="n">
-        <v>1745406</v>
+        <v>610156</v>
       </c>
       <c r="M4" t="n">
-        <v>600300</v>
+        <v>199150</v>
       </c>
       <c r="N4" t="n">
-        <v>76737</v>
+        <v>26037</v>
       </c>
       <c r="O4" t="n">
-        <v>271551</v>
+        <v>93789</v>
       </c>
       <c r="P4" t="n">
-        <v>69276</v>
+        <v>23078</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999971985816956</v>
+        <v>0.9999940991401672</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9196151494979858</v>
+        <v>0.9165363907814026</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8349859714508057</v>
+        <v>0.8292345404624939</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7634439468383789</v>
+        <v>0.7578555941581726</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4851655960083008</v>
+        <v>0.4596886336803436</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8248312473297119</v>
+        <v>0.8199261426925659</v>
       </c>
       <c r="W4" t="n">
-        <v>0.871976912021637</v>
+        <v>0.8673509955406189</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>609497</v>
+        <v>204218</v>
       </c>
       <c r="Z4" t="n">
-        <v>8878131</v>
+        <v>2970254</v>
       </c>
       <c r="AA4" t="n">
-        <v>247989</v>
+        <v>83015</v>
       </c>
       <c r="AB4" t="n">
-        <v>16406</v>
+        <v>5489</v>
       </c>
       <c r="AC4" t="n">
-        <v>3432</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>204</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>652858</v>
+        <v>218736</v>
       </c>
       <c r="AG4" t="n">
-        <v>864862</v>
+        <v>289099</v>
       </c>
       <c r="AH4" t="n">
-        <v>395847</v>
+        <v>132377</v>
       </c>
       <c r="AI4" t="n">
-        <v>89961</v>
+        <v>30069</v>
       </c>
       <c r="AJ4" t="n">
-        <v>149468</v>
+        <v>49876</v>
       </c>
       <c r="AK4" t="n">
-        <v>39762</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9571335315704346</v>
+        <v>0.9570662379264832</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106404781341553</v>
+        <v>0.910625696182251</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8579724431037903</v>
+        <v>0.8577942252159119</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6624025702476501</v>
+        <v>0.6621472835540771</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.901857852935791</v>
+        <v>0.9018250107765198</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313915967941284</v>
+        <v>0.9313808679580688</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>37595</v>
+        <v>13333</v>
       </c>
       <c r="E5" t="n">
-        <v>467324</v>
+        <v>162832</v>
       </c>
       <c r="F5" t="n">
-        <v>2094633</v>
+        <v>690209</v>
       </c>
       <c r="G5" t="n">
-        <v>34968</v>
+        <v>11849</v>
       </c>
       <c r="H5" t="n">
-        <v>150083</v>
+        <v>51680</v>
       </c>
       <c r="I5" t="n">
-        <v>7778</v>
+        <v>2216</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1234327</v>
+        <v>427837</v>
       </c>
       <c r="L5" t="n">
-        <v>1512644</v>
+        <v>520053</v>
       </c>
       <c r="M5" t="n">
-        <v>697760</v>
+        <v>241911</v>
       </c>
       <c r="N5" t="n">
-        <v>156848</v>
+        <v>54759</v>
       </c>
       <c r="O5" t="n">
-        <v>264513</v>
+        <v>90231</v>
       </c>
       <c r="P5" t="n">
-        <v>78066</v>
+        <v>27604</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999978542327881</v>
+        <v>0.9999954700469971</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9505700469017029</v>
+        <v>0.948685348033905</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9333176016807556</v>
+        <v>0.9307876825332642</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9734326601028442</v>
+        <v>0.972990095615387</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9952192306518555</v>
+        <v>0.99505215883255</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9890283942222595</v>
+        <v>0.9887309074401855</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9969843626022339</v>
+        <v>0.9968963265419006</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>23924</v>
+        <v>8010</v>
       </c>
       <c r="Z5" t="n">
-        <v>254266</v>
+        <v>84966</v>
       </c>
       <c r="AA5" t="n">
-        <v>2395233</v>
+        <v>799435</v>
       </c>
       <c r="AB5" t="n">
-        <v>29769</v>
+        <v>9941</v>
       </c>
       <c r="AC5" t="n">
-        <v>87302</v>
+        <v>29135</v>
       </c>
       <c r="AD5" t="n">
-        <v>1899</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>637970</v>
+        <v>213300</v>
       </c>
       <c r="AG5" t="n">
-        <v>877528</v>
+        <v>293938</v>
       </c>
       <c r="AH5" t="n">
-        <v>397160</v>
+        <v>132685</v>
       </c>
       <c r="AI5" t="n">
-        <v>90181</v>
+        <v>30134</v>
       </c>
       <c r="AJ5" t="n">
-        <v>150119</v>
+        <v>50081</v>
       </c>
       <c r="AK5" t="n">
-        <v>39800</v>
+        <v>13273</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735806584358215</v>
+        <v>0.9735427498817444</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643385410308838</v>
+        <v>0.9642956852912903</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837695360183716</v>
+        <v>0.9837679862976074</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963130354881287</v>
+        <v>0.9963132739067078</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.993868350982666</v>
+        <v>0.9938787817955017</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983716011047363</v>
+        <v>0.9983755350112915</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>26213</v>
+        <v>9328</v>
       </c>
       <c r="E6" t="n">
-        <v>45718</v>
+        <v>18520</v>
       </c>
       <c r="F6" t="n">
-        <v>53766</v>
+        <v>15946</v>
       </c>
       <c r="G6" t="n">
-        <v>110062</v>
+        <v>34370</v>
       </c>
       <c r="H6" t="n">
-        <v>28971</v>
+        <v>10304</v>
       </c>
       <c r="I6" t="n">
-        <v>2156</v>
+        <v>645</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>19270</v>
+        <v>6452</v>
       </c>
       <c r="Z6" t="n">
-        <v>15989</v>
+        <v>5347</v>
       </c>
       <c r="AA6" t="n">
-        <v>32568</v>
+        <v>10875</v>
       </c>
       <c r="AB6" t="n">
-        <v>176729</v>
+        <v>58995</v>
       </c>
       <c r="AC6" t="n">
-        <v>20911</v>
+        <v>6979</v>
       </c>
       <c r="AD6" t="n">
-        <v>1443</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D7" t="n">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="E7" t="n">
-        <v>18546</v>
+        <v>5170</v>
       </c>
       <c r="F7" t="n">
-        <v>157904</v>
+        <v>54483</v>
       </c>
       <c r="G7" t="n">
-        <v>29928</v>
+        <v>10617</v>
       </c>
       <c r="H7" t="n">
-        <v>1262104</v>
+        <v>418947</v>
       </c>
       <c r="I7" t="n">
-        <v>58025</v>
+        <v>19897</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>2427</v>
+        <v>809</v>
       </c>
       <c r="AA7" t="n">
-        <v>88780</v>
+        <v>29617</v>
       </c>
       <c r="AB7" t="n">
-        <v>22703</v>
+        <v>7585</v>
       </c>
       <c r="AC7" t="n">
-        <v>1376498</v>
+        <v>459097</v>
       </c>
       <c r="AD7" t="n">
-        <v>36126</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D8" t="n">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="E8" t="n">
-        <v>916</v>
+        <v>233</v>
       </c>
       <c r="F8" t="n">
-        <v>4090</v>
+        <v>1233</v>
       </c>
       <c r="G8" t="n">
-        <v>1371</v>
+        <v>456</v>
       </c>
       <c r="H8" t="n">
-        <v>71602</v>
+        <v>25642</v>
       </c>
       <c r="I8" t="n">
-        <v>501780</v>
+        <v>165697</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>243</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>990</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>795</v>
+        <v>265</v>
       </c>
       <c r="AC8" t="n">
-        <v>37688</v>
+        <v>12569</v>
       </c>
       <c r="AD8" t="n">
-        <v>540046</v>
+        <v>180028</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
